--- a/exports/trend_1d/ASIANPAINT_full_report.xlsx
+++ b/exports/trend_1d/ASIANPAINT_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q71"/>
+  <dimension ref="A1:U71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,28 +557,28 @@
         <v>8.66</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42034</v>
+        <v>42037</v>
       </c>
       <c r="H2" t="n">
-        <v>857.75</v>
+        <v>808.1</v>
       </c>
       <c r="I2" t="n">
         <v>833.18524167589</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K2" t="n">
-        <v>2.19</v>
+        <v>-3.72</v>
       </c>
       <c r="L2" t="n">
-        <v>1.17</v>
+        <v>4.27</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="N2" t="n">
-        <v>3.18</v>
+        <v>5.79</v>
       </c>
       <c r="O2" t="n">
         <v>-0.39</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42033</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -591,22 +626,22 @@
         <v>13.77</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42101</v>
+        <v>42102</v>
       </c>
       <c r="H3" t="n">
-        <v>835.2</v>
+        <v>846.85</v>
       </c>
       <c r="I3" t="n">
         <v>843.6731546912874</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K3" t="n">
-        <v>-3.35</v>
+        <v>-4.8</v>
       </c>
       <c r="L3" t="n">
-        <v>5.32</v>
+        <v>5.68</v>
       </c>
       <c r="M3" t="n">
         <v>2.06</v>
@@ -621,7 +656,19 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42061</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -648,22 +695,22 @@
         <v>7.12</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42114</v>
+        <v>42115</v>
       </c>
       <c r="H4" t="n">
-        <v>808.95</v>
+        <v>796.5</v>
       </c>
       <c r="I4" t="n">
         <v>802.3257654749787</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K4" t="n">
-        <v>-4.48</v>
+        <v>-5.95</v>
       </c>
       <c r="L4" t="n">
-        <v>5.53</v>
+        <v>6.48</v>
       </c>
       <c r="M4" t="n">
         <v>0.48</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42124</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>8.710000000000001</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42186</v>
+        <v>42187</v>
       </c>
       <c r="H5" t="n">
-        <v>760.8</v>
+        <v>762.9</v>
       </c>
       <c r="I5" t="n">
         <v>760.9588595878133</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K5" t="n">
-        <v>4.48</v>
+        <v>4.22</v>
       </c>
       <c r="L5" t="n">
         <v>2.7</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42124</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>4</v>
+      </c>
+      <c r="U5" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -762,28 +833,28 @@
         <v>6.44</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42237</v>
+        <v>42240</v>
       </c>
       <c r="H6" t="n">
-        <v>886.75</v>
+        <v>837.5</v>
       </c>
       <c r="I6" t="n">
         <v>841.9022975398276</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K6" t="n">
-        <v>16.23</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="L6" t="n">
         <v>0.59</v>
       </c>
       <c r="M6" t="n">
-        <v>1</v>
+        <v>3.24</v>
       </c>
       <c r="N6" t="n">
-        <v>4.25</v>
+        <v>5.55</v>
       </c>
       <c r="O6" t="n">
         <v>0.28</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42215</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,22 +902,22 @@
         <v>11.98</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42284</v>
+        <v>42285</v>
       </c>
       <c r="H7" t="n">
-        <v>865.05</v>
+        <v>874.15</v>
       </c>
       <c r="I7" t="n">
         <v>872.7728224282733</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K7" t="n">
-        <v>-3.29</v>
+        <v>-4.38</v>
       </c>
       <c r="L7" t="n">
-        <v>4.74</v>
+        <v>5.07</v>
       </c>
       <c r="M7" t="n">
         <v>1.49</v>
@@ -849,7 +932,19 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42243</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -876,28 +971,28 @@
         <v>8.380000000000001</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42300</v>
+        <v>42303</v>
       </c>
       <c r="H8" t="n">
-        <v>858.6</v>
+        <v>817.7</v>
       </c>
       <c r="I8" t="n">
         <v>818.7643064202646</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.78</v>
+        <v>-6.46</v>
       </c>
       <c r="L8" t="n">
-        <v>3.21</v>
+        <v>7.2</v>
       </c>
       <c r="M8" t="n">
-        <v>0.6</v>
+        <v>3.33</v>
       </c>
       <c r="N8" t="n">
-        <v>2.33</v>
+        <v>4.76</v>
       </c>
       <c r="O8" t="n">
         <v>1.05</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42306</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -933,22 +1040,22 @@
         <v>9.99</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42332</v>
+        <v>42334</v>
       </c>
       <c r="H9" t="n">
-        <v>856.6</v>
+        <v>861.85</v>
       </c>
       <c r="I9" t="n">
         <v>857.2496192958591</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="K9" t="n">
-        <v>-4.76</v>
+        <v>-5.4</v>
       </c>
       <c r="L9" t="n">
-        <v>5.39</v>
+        <v>5.9</v>
       </c>
       <c r="M9" t="n">
         <v>1.28</v>
@@ -963,7 +1070,19 @@
         <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42306</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,22 +1109,22 @@
         <v>6.33</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>42387</v>
+        <v>42388</v>
       </c>
       <c r="H10" t="n">
-        <v>850.3</v>
+        <v>845.55</v>
       </c>
       <c r="I10" t="n">
         <v>848.0700523043884</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.34</v>
+        <v>-1.89</v>
       </c>
       <c r="L10" t="n">
-        <v>3.76</v>
+        <v>4.16</v>
       </c>
       <c r="M10" t="n">
         <v>0.58</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42369</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1047,22 +1178,22 @@
         <v>9.529999999999999</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>42500</v>
+        <v>42501</v>
       </c>
       <c r="H11" t="n">
-        <v>898.35</v>
+        <v>907.85</v>
       </c>
       <c r="I11" t="n">
         <v>906.939785861804</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="K11" t="n">
-        <v>-6.24</v>
+        <v>-7.37</v>
       </c>
       <c r="L11" t="n">
-        <v>8.08</v>
+        <v>8.69</v>
       </c>
       <c r="M11" t="n">
         <v>2.07</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>74</v>
+        <v>75</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>42397</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>5</v>
+      </c>
+      <c r="U11" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>6.89</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>42664</v>
+        <v>42667</v>
       </c>
       <c r="H12" t="n">
-        <v>1153.5</v>
+        <v>1127.5</v>
       </c>
       <c r="I12" t="n">
         <v>1140.129615805791</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="K12" t="n">
-        <v>27.06</v>
+        <v>24.19</v>
       </c>
       <c r="L12" t="n">
         <v>2.24</v>
@@ -1125,7 +1268,7 @@
         <v>1.95</v>
       </c>
       <c r="N12" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="O12" t="n">
         <v>1.06</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>112</v>
+        <v>113</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>42516</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>6</v>
+      </c>
+      <c r="U12" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>8.279999999999999</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>42748</v>
+        <v>42751</v>
       </c>
       <c r="H13" t="n">
-        <v>933.25</v>
+        <v>935.25</v>
       </c>
       <c r="I13" t="n">
         <v>935.2432690341229</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="K13" t="n">
-        <v>17.23</v>
+        <v>17.05</v>
       </c>
       <c r="L13" t="n">
         <v>3.06</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>42670</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>4</v>
+      </c>
+      <c r="U13" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>6.09</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>42877</v>
+        <v>42878</v>
       </c>
       <c r="H14" t="n">
-        <v>1112.55</v>
+        <v>1098.9</v>
       </c>
       <c r="I14" t="n">
         <v>1102.059366807137</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="K14" t="n">
-        <v>18.96</v>
+        <v>17.5</v>
       </c>
       <c r="L14" t="n">
         <v>0.89</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>85</v>
+        <v>86</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>42760</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>5</v>
+      </c>
+      <c r="U14" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="15">
@@ -1275,28 +1454,28 @@
         <v>8.69</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>42978</v>
+        <v>42979</v>
       </c>
       <c r="H15" t="n">
-        <v>1168.55</v>
+        <v>1215.9</v>
       </c>
       <c r="I15" t="n">
         <v>1169.657282984936</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K15" t="n">
-        <v>-6.34</v>
+        <v>-10.65</v>
       </c>
       <c r="L15" t="n">
-        <v>10.61</v>
+        <v>10.93</v>
       </c>
       <c r="M15" t="n">
         <v>8.960000000000001</v>
       </c>
       <c r="N15" t="n">
-        <v>2.02</v>
+        <v>4.05</v>
       </c>
       <c r="O15" t="n">
         <v>-1.23</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>70</v>
+        <v>71</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>42880</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>5</v>
+      </c>
+      <c r="U15" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="16">
@@ -1332,28 +1523,28 @@
         <v>7.91</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>43003</v>
+        <v>43004</v>
       </c>
       <c r="H16" t="n">
-        <v>1196.95</v>
+        <v>1174</v>
       </c>
       <c r="I16" t="n">
         <v>1191.050152883147</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.56</v>
+        <v>-3.45</v>
       </c>
       <c r="L16" t="n">
-        <v>4.1</v>
+        <v>4.27</v>
       </c>
       <c r="M16" t="n">
         <v>1.25</v>
       </c>
       <c r="N16" t="n">
-        <v>1.55</v>
+        <v>1.92</v>
       </c>
       <c r="O16" t="n">
         <v>4.05</v>
@@ -1362,7 +1553,19 @@
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>43006</v>
+      </c>
+      <c r="S16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1389,28 +1592,28 @@
         <v>6.13</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>43031</v>
+        <v>43032</v>
       </c>
       <c r="H17" t="n">
-        <v>1174.15</v>
+        <v>1222.9</v>
       </c>
       <c r="I17" t="n">
         <v>1209.339431117318</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.01</v>
+        <v>-4.17</v>
       </c>
       <c r="L17" t="n">
-        <v>2.21</v>
+        <v>5.11</v>
       </c>
       <c r="M17" t="n">
         <v>1.08</v>
       </c>
       <c r="N17" t="n">
-        <v>2.23</v>
+        <v>4.15</v>
       </c>
       <c r="O17" t="n">
         <v>-1.92</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>43006</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,22 +1661,22 @@
         <v>8.109999999999999</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>43070</v>
+        <v>43073</v>
       </c>
       <c r="H18" t="n">
-        <v>1133.75</v>
+        <v>1121</v>
       </c>
       <c r="I18" t="n">
         <v>1129.718676002473</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="K18" t="n">
-        <v>-7.29</v>
+        <v>-8.33</v>
       </c>
       <c r="L18" t="n">
-        <v>7.58</v>
+        <v>8.66</v>
       </c>
       <c r="M18" t="n">
         <v>0.64</v>
@@ -1476,7 +1691,19 @@
         <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>43034</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1503,22 +1730,22 @@
         <v>7.03</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>43103</v>
+        <v>43104</v>
       </c>
       <c r="H19" t="n">
-        <v>1141.9</v>
+        <v>1172.05</v>
       </c>
       <c r="I19" t="n">
         <v>1171.668185256719</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.86</v>
+        <v>-4.55</v>
       </c>
       <c r="L19" t="n">
-        <v>4.59</v>
+        <v>5.08</v>
       </c>
       <c r="M19" t="n">
         <v>1.04</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>43097</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,28 +1799,28 @@
         <v>6.37</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>43129</v>
+        <v>43130</v>
       </c>
       <c r="H20" t="n">
-        <v>1152.05</v>
+        <v>1126.7</v>
       </c>
       <c r="I20" t="n">
         <v>1131.272886032016</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.71</v>
+        <v>-3.87</v>
       </c>
       <c r="L20" t="n">
-        <v>2.44</v>
+        <v>4.15</v>
       </c>
       <c r="M20" t="n">
         <v>0.59</v>
       </c>
       <c r="N20" t="n">
-        <v>1.61</v>
+        <v>2.2</v>
       </c>
       <c r="O20" t="n">
         <v>2.64</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>43125</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>6.82</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>43201</v>
+        <v>43202</v>
       </c>
       <c r="H21" t="n">
-        <v>1155.85</v>
+        <v>1165.2</v>
       </c>
       <c r="I21" t="n">
         <v>1161.730809254383</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K21" t="n">
-        <v>-2.59</v>
+        <v>-3.42</v>
       </c>
       <c r="L21" t="n">
         <v>3.98</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>43153</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>6.41</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>43346</v>
+        <v>43347</v>
       </c>
       <c r="H22" t="n">
-        <v>1361.6</v>
+        <v>1311.3</v>
       </c>
       <c r="I22" t="n">
         <v>1352.438451219077</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="K22" t="n">
-        <v>16.86</v>
+        <v>12.54</v>
       </c>
       <c r="L22" t="n">
         <v>1.97</v>
@@ -1695,7 +1958,7 @@
         <v>1.22</v>
       </c>
       <c r="N22" t="n">
-        <v>1.69</v>
+        <v>3.69</v>
       </c>
       <c r="O22" t="n">
         <v>0.8100000000000001</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>100</v>
+        <v>101</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>43216</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>6</v>
+      </c>
+      <c r="U22" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="23">
@@ -1731,25 +2006,25 @@
         <v>8.5</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>43417</v>
+        <v>43418</v>
       </c>
       <c r="H23" t="n">
-        <v>1284.9</v>
+        <v>1320.55</v>
       </c>
       <c r="I23" t="n">
         <v>1296.703210215538</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K23" t="n">
-        <v>2.01</v>
+        <v>-0.71</v>
       </c>
       <c r="L23" t="n">
         <v>4.06</v>
       </c>
       <c r="M23" t="n">
-        <v>1.99</v>
+        <v>2.11</v>
       </c>
       <c r="N23" t="n">
         <v>4.61</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>43370</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>9.699999999999999</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>43564</v>
+        <v>43565</v>
       </c>
       <c r="H24" t="n">
-        <v>1444.85</v>
+        <v>1409.85</v>
       </c>
       <c r="I24" t="n">
         <v>1431.09856033974</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="K24" t="n">
-        <v>9.41</v>
+        <v>6.76</v>
       </c>
       <c r="L24" t="n">
         <v>5.18</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>101</v>
+        <v>102</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>43433</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>6</v>
+      </c>
+      <c r="U24" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>8.15</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>43615</v>
+        <v>43616</v>
       </c>
       <c r="H25" t="n">
-        <v>1374.6</v>
+        <v>1407.3</v>
       </c>
       <c r="I25" t="n">
         <v>1398.046263798888</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K25" t="n">
-        <v>2.5</v>
+        <v>0.18</v>
       </c>
       <c r="L25" t="n">
         <v>4.97</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>43580</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -1902,22 +2213,22 @@
         <v>7.35</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>43654</v>
+        <v>43655</v>
       </c>
       <c r="H26" t="n">
-        <v>1340.25</v>
+        <v>1321</v>
       </c>
       <c r="I26" t="n">
         <v>1339.65261760629</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K26" t="n">
-        <v>-4.76</v>
+        <v>-6.13</v>
       </c>
       <c r="L26" t="n">
-        <v>5.3</v>
+        <v>8.25</v>
       </c>
       <c r="M26" t="n">
         <v>1.13</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>43643</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1959,28 +2282,28 @@
         <v>5.86</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>43665</v>
+        <v>43668</v>
       </c>
       <c r="H27" t="n">
-        <v>1369.1</v>
+        <v>1404.2</v>
       </c>
       <c r="I27" t="n">
         <v>1398.448361874822</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K27" t="n">
-        <v>-3.64</v>
+        <v>-6.3</v>
       </c>
       <c r="L27" t="n">
-        <v>6.35</v>
+        <v>6.74</v>
       </c>
       <c r="M27" t="n">
         <v>0.37</v>
       </c>
       <c r="N27" t="n">
-        <v>2.21</v>
+        <v>2.56</v>
       </c>
       <c r="O27" t="n">
         <v>-1.44</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>43671</v>
+      </c>
+      <c r="S27" t="b">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>7.9</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>43712</v>
+        <v>43713</v>
       </c>
       <c r="H28" t="n">
-        <v>1535.15</v>
+        <v>1519.75</v>
       </c>
       <c r="I28" t="n">
         <v>1527.475283388383</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K28" t="n">
-        <v>9.33</v>
+        <v>8.23</v>
       </c>
       <c r="L28" t="n">
         <v>3.22</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>43671</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>3</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -2073,28 +2420,28 @@
         <v>6.87</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>43727</v>
+        <v>43728</v>
       </c>
       <c r="H29" t="n">
-        <v>1553.9</v>
+        <v>1671</v>
       </c>
       <c r="I29" t="n">
         <v>1605.812680360409</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K29" t="n">
-        <v>-2.25</v>
+        <v>-9.949999999999999</v>
       </c>
       <c r="L29" t="n">
-        <v>3.31</v>
+        <v>13.52</v>
       </c>
       <c r="M29" t="n">
         <v>0.73</v>
       </c>
       <c r="N29" t="n">
-        <v>1.35</v>
+        <v>7.54</v>
       </c>
       <c r="O29" t="n">
         <v>-1</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>43734</v>
+      </c>
+      <c r="S29" t="b">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>10.17</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>43790</v>
+        <v>43791</v>
       </c>
       <c r="H30" t="n">
-        <v>1720.35</v>
+        <v>1682.75</v>
       </c>
       <c r="I30" t="n">
         <v>1705.323815840522</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K30" t="n">
-        <v>2.95</v>
+        <v>0.7</v>
       </c>
       <c r="L30" t="n">
         <v>7.71</v>
@@ -2160,7 +2519,19 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>43734</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>3</v>
+      </c>
+      <c r="U30" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -2187,22 +2558,22 @@
         <v>6.74</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>43817</v>
+        <v>43818</v>
       </c>
       <c r="H31" t="n">
-        <v>1778.45</v>
+        <v>1803.1</v>
       </c>
       <c r="I31" t="n">
         <v>1796.232392419085</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K31" t="n">
-        <v>-5.69</v>
+        <v>-7.15</v>
       </c>
       <c r="L31" t="n">
-        <v>5.9</v>
+        <v>7.43</v>
       </c>
       <c r="M31" t="n">
         <v>0.49</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>43797</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,28 +2627,28 @@
         <v>5.71</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>43833</v>
+        <v>43836</v>
       </c>
       <c r="H32" t="n">
-        <v>1751.4</v>
+        <v>1707.15</v>
       </c>
       <c r="I32" t="n">
         <v>1730.001121775188</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K32" t="n">
-        <v>-2.87</v>
+        <v>-5.32</v>
       </c>
       <c r="L32" t="n">
-        <v>3.11</v>
+        <v>6.05</v>
       </c>
       <c r="M32" t="n">
-        <v>0.61</v>
+        <v>0.77</v>
       </c>
       <c r="N32" t="n">
-        <v>2.19</v>
+        <v>2.53</v>
       </c>
       <c r="O32" t="n">
         <v>1.39</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>43825</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2301,22 +2696,22 @@
         <v>5.77</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>43843</v>
+        <v>43844</v>
       </c>
       <c r="H33" t="n">
-        <v>1804.9</v>
+        <v>1819.15</v>
       </c>
       <c r="I33" t="n">
         <v>1805.704674392672</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K33" t="n">
-        <v>-5.73</v>
+        <v>-6.56</v>
       </c>
       <c r="L33" t="n">
-        <v>5.9</v>
+        <v>6.71</v>
       </c>
       <c r="M33" t="n">
         <v>1.98</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>43860</v>
+      </c>
+      <c r="S33" t="b">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -2358,28 +2765,28 @@
         <v>5.27</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>43861</v>
+        <v>43862</v>
       </c>
       <c r="H34" t="n">
-        <v>1795.65</v>
+        <v>1755.35</v>
       </c>
       <c r="I34" t="n">
         <v>1760.431976263639</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K34" t="n">
-        <v>-1.29</v>
+        <v>-3.51</v>
       </c>
       <c r="L34" t="n">
-        <v>3.41</v>
+        <v>3.97</v>
       </c>
       <c r="M34" t="n">
         <v>0.48</v>
       </c>
       <c r="N34" t="n">
-        <v>2.06</v>
+        <v>2.24</v>
       </c>
       <c r="O34" t="n">
         <v>0.79</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>43860</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2415,22 +2834,22 @@
         <v>7.37</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>43864</v>
+        <v>43865</v>
       </c>
       <c r="H35" t="n">
-        <v>1867.65</v>
+        <v>1891.3</v>
       </c>
       <c r="I35" t="n">
         <v>1884.798944264407</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K35" t="n">
-        <v>-6.4</v>
+        <v>-7.74</v>
       </c>
       <c r="L35" t="n">
-        <v>6.7</v>
+        <v>8.06</v>
       </c>
       <c r="M35" t="n">
         <v>0.77</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>43888</v>
+      </c>
+      <c r="S35" t="b">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>7.54</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>43903</v>
+        <v>43906</v>
       </c>
       <c r="H36" t="n">
-        <v>1797.7</v>
+        <v>1683.4</v>
       </c>
       <c r="I36" t="n">
         <v>1785.405476017055</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="K36" t="n">
-        <v>-4.95</v>
+        <v>-10.99</v>
       </c>
       <c r="L36" t="n">
         <v>11.71</v>
@@ -2493,7 +2924,7 @@
         <v>3.17</v>
       </c>
       <c r="N36" t="n">
-        <v>2.49</v>
+        <v>6.36</v>
       </c>
       <c r="O36" t="n">
         <v>1.27</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>43888</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>14.51</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>43944</v>
+        <v>43945</v>
       </c>
       <c r="H37" t="n">
-        <v>1821.65</v>
+        <v>1827.55</v>
       </c>
       <c r="I37" t="n">
         <v>1822.606723334077</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K37" t="n">
-        <v>-8.210000000000001</v>
+        <v>-8.56</v>
       </c>
       <c r="L37" t="n">
         <v>9.619999999999999</v>
@@ -2559,7 +3002,19 @@
         <v>1</v>
       </c>
       <c r="Q37" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>43916</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,22 +3041,22 @@
         <v>12.56</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>43955</v>
+        <v>43956</v>
       </c>
       <c r="H38" t="n">
-        <v>1676.8</v>
+        <v>1619.15</v>
       </c>
       <c r="I38" t="n">
         <v>1619.916988491757</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K38" t="n">
-        <v>-8.25</v>
+        <v>-11.4</v>
       </c>
       <c r="L38" t="n">
-        <v>8.539999999999999</v>
+        <v>13.64</v>
       </c>
       <c r="M38" t="n">
         <v>2.31</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>43951</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,22 +3110,22 @@
         <v>15.39</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>43979</v>
+        <v>43980</v>
       </c>
       <c r="H39" t="n">
-        <v>1643.6</v>
+        <v>1683.1</v>
       </c>
       <c r="I39" t="n">
         <v>1677.103801469666</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K39" t="n">
-        <v>-1.51</v>
+        <v>-3.95</v>
       </c>
       <c r="L39" t="n">
-        <v>4.55</v>
+        <v>4.93</v>
       </c>
       <c r="M39" t="n">
         <v>3.71</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>43979</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>11.13</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>44209</v>
+        <v>44210</v>
       </c>
       <c r="H40" t="n">
-        <v>2703.7</v>
+        <v>2663.9</v>
       </c>
       <c r="I40" t="n">
         <v>2684.975764103638</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="K40" t="n">
-        <v>60.64</v>
+        <v>58.27</v>
       </c>
       <c r="L40" t="n">
         <v>6.27</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>161</v>
+        <v>162</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>44007</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>8</v>
+      </c>
+      <c r="U40" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>8.67</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>44281</v>
+        <v>44285</v>
       </c>
       <c r="H41" t="n">
-        <v>2505.15</v>
+        <v>2578.05</v>
       </c>
       <c r="I41" t="n">
         <v>2536.627897671884</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="K41" t="n">
-        <v>5.96</v>
+        <v>3.22</v>
       </c>
       <c r="L41" t="n">
         <v>5.75</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>44224</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>4</v>
+      </c>
+      <c r="U41" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>9.369999999999999</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>44468</v>
+        <v>44469</v>
       </c>
       <c r="H42" t="n">
-        <v>3323.05</v>
+        <v>3244.65</v>
       </c>
       <c r="I42" t="n">
         <v>3245.964171340846</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="K42" t="n">
-        <v>28.9</v>
+        <v>25.86</v>
       </c>
       <c r="L42" t="n">
         <v>3.63</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>125</v>
+        <v>126</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>44315</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>6</v>
+      </c>
+      <c r="U42" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>8.029999999999999</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>44516</v>
+        <v>44517</v>
       </c>
       <c r="H43" t="n">
-        <v>3151.7</v>
+        <v>3230.25</v>
       </c>
       <c r="I43" t="n">
         <v>3191.39331294182</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K43" t="n">
-        <v>2.86</v>
+        <v>0.44</v>
       </c>
       <c r="L43" t="n">
         <v>3.52</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>44497</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,22 +3455,22 @@
         <v>8</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>44536</v>
+        <v>44537</v>
       </c>
       <c r="H44" t="n">
-        <v>3038.3</v>
+        <v>3030.35</v>
       </c>
       <c r="I44" t="n">
         <v>3034.35466744468</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K44" t="n">
-        <v>-5.94</v>
+        <v>-6.19</v>
       </c>
       <c r="L44" t="n">
-        <v>6.25</v>
+        <v>6.62</v>
       </c>
       <c r="M44" t="n">
         <v>1.38</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>44525</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2985,28 +3524,28 @@
         <v>7.84</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>44539</v>
+        <v>44540</v>
       </c>
       <c r="H45" t="n">
-        <v>3178.7</v>
+        <v>3283.15</v>
       </c>
       <c r="I45" t="n">
         <v>3267.924405614147</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K45" t="n">
-        <v>-4.9</v>
+        <v>-8.34</v>
       </c>
       <c r="L45" t="n">
-        <v>5.04</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="M45" t="n">
         <v>1.41</v>
       </c>
       <c r="N45" t="n">
-        <v>2.58</v>
+        <v>3.29</v>
       </c>
       <c r="O45" t="n">
         <v>-0.26</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>44560</v>
+      </c>
+      <c r="S45" t="b">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>1</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>8.789999999999999</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>44579</v>
+        <v>44580</v>
       </c>
       <c r="H46" t="n">
-        <v>3373.7</v>
+        <v>3280.4</v>
       </c>
       <c r="I46" t="n">
         <v>3362.258613769947</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K46" t="n">
-        <v>2.76</v>
+        <v>-0.08</v>
       </c>
       <c r="L46" t="n">
         <v>3.18</v>
@@ -3063,7 +3614,7 @@
         <v>1.01</v>
       </c>
       <c r="N46" t="n">
-        <v>2.66</v>
+        <v>2.77</v>
       </c>
       <c r="O46" t="n">
         <v>3.29</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>44560</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>8.050000000000001</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>44635</v>
+        <v>44636</v>
       </c>
       <c r="H47" t="n">
-        <v>2987.15</v>
+        <v>3042</v>
       </c>
       <c r="I47" t="n">
         <v>3038.440720394527</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K47" t="n">
-        <v>8.94</v>
+        <v>7.27</v>
       </c>
       <c r="L47" t="n">
         <v>2.73</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>3</v>
+      </c>
+      <c r="U47" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="48">
@@ -3156,25 +3731,25 @@
         <v>11.26</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>44686</v>
+        <v>44687</v>
       </c>
       <c r="H48" t="n">
-        <v>3076.55</v>
+        <v>3016.25</v>
       </c>
       <c r="I48" t="n">
         <v>3023.966105975142</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K48" t="n">
-        <v>1.14</v>
+        <v>-0.85</v>
       </c>
       <c r="L48" t="n">
         <v>3.01</v>
       </c>
       <c r="M48" t="n">
-        <v>1.57</v>
+        <v>1.84</v>
       </c>
       <c r="N48" t="n">
         <v>3.1</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>3</v>
+      </c>
+      <c r="U48" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>8.09</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>44748</v>
+        <v>44749</v>
       </c>
       <c r="H49" t="n">
-        <v>2861.4</v>
+        <v>2891.4</v>
       </c>
       <c r="I49" t="n">
         <v>2862.629148803981</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K49" t="n">
-        <v>5.13</v>
+        <v>4.14</v>
       </c>
       <c r="L49" t="n">
         <v>5.69</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>3</v>
+      </c>
+      <c r="U49" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>7.49</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>44798</v>
+        <v>44799</v>
       </c>
       <c r="H50" t="n">
-        <v>3362.5</v>
+        <v>3323.55</v>
       </c>
       <c r="I50" t="n">
         <v>3344.946512523809</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K50" t="n">
-        <v>16.29</v>
+        <v>14.95</v>
       </c>
       <c r="L50" t="n">
         <v>1.76</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>3</v>
+      </c>
+      <c r="U50" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="51">
@@ -3327,28 +3938,28 @@
         <v>7.09</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>44831</v>
+        <v>44832</v>
       </c>
       <c r="H51" t="n">
-        <v>3470.65</v>
+        <v>3570.65</v>
       </c>
       <c r="I51" t="n">
         <v>3510.079256049475</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K51" t="n">
-        <v>-4.43</v>
+        <v>-7.43</v>
       </c>
       <c r="L51" t="n">
-        <v>5.31</v>
+        <v>7.8</v>
       </c>
       <c r="M51" t="n">
         <v>1.46</v>
       </c>
       <c r="N51" t="n">
-        <v>2.38</v>
+        <v>2.88</v>
       </c>
       <c r="O51" t="n">
         <v>-1.16</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S51" t="b">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>1</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -3384,22 +4007,22 @@
         <v>9.42</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>44846</v>
+        <v>44847</v>
       </c>
       <c r="H52" t="n">
-        <v>3248.2</v>
+        <v>3209</v>
       </c>
       <c r="I52" t="n">
         <v>3234.29152638223</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K52" t="n">
-        <v>-9.029999999999999</v>
+        <v>-10.13</v>
       </c>
       <c r="L52" t="n">
-        <v>10.21</v>
+        <v>10.55</v>
       </c>
       <c r="M52" t="n">
         <v>1.91</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>8.98</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45040</v>
+        <v>45041</v>
       </c>
       <c r="H53" t="n">
-        <v>2891.1</v>
+        <v>2898</v>
       </c>
       <c r="I53" t="n">
         <v>2895.755906369915</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="K53" t="n">
-        <v>9.91</v>
+        <v>9.69</v>
       </c>
       <c r="L53" t="n">
         <v>1.53</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>130</v>
+        <v>131</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>7</v>
+      </c>
+      <c r="U53" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>5.23</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45132</v>
+        <v>45133</v>
       </c>
       <c r="H54" t="n">
-        <v>3400.4</v>
+        <v>3373</v>
       </c>
       <c r="I54" t="n">
         <v>3373.387699906732</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K54" t="n">
-        <v>17.34</v>
+        <v>16.39</v>
       </c>
       <c r="L54" t="n">
         <v>1.77</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>4</v>
+      </c>
+      <c r="U54" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>6.32</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45243</v>
+        <v>45245</v>
       </c>
       <c r="H55" t="n">
-        <v>3085.6</v>
+        <v>3116.2</v>
       </c>
       <c r="I55" t="n">
         <v>3105.793939310377</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="K55" t="n">
-        <v>8.52</v>
+        <v>7.61</v>
       </c>
       <c r="L55" t="n">
         <v>1.22</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>76</v>
+        <v>77</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>5</v>
+      </c>
+      <c r="U55" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>4.92</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45307</v>
+        <v>45308</v>
       </c>
       <c r="H56" t="n">
-        <v>3296.9</v>
+        <v>3242.3</v>
       </c>
       <c r="I56" t="n">
         <v>3252.37717876646</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K56" t="n">
-        <v>5.8</v>
+        <v>4.05</v>
       </c>
       <c r="L56" t="n">
         <v>1.2</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>3</v>
+      </c>
+      <c r="U56" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>5.03</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45412</v>
+        <v>45414</v>
       </c>
       <c r="H57" t="n">
-        <v>2875.9</v>
+        <v>2975.4</v>
       </c>
       <c r="I57" t="n">
         <v>2938.307918508927</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="K57" t="n">
-        <v>11.3</v>
+        <v>8.23</v>
       </c>
       <c r="L57" t="n">
         <v>1.91</v>
@@ -3690,7 +4373,7 @@
         <v>1.35</v>
       </c>
       <c r="N57" t="n">
-        <v>1.71</v>
+        <v>3.46</v>
       </c>
       <c r="O57" t="n">
         <v>-1.66</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>70</v>
+        <v>71</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>5</v>
+      </c>
+      <c r="U57" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="58">
@@ -3726,28 +4421,28 @@
         <v>6.59</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45420</v>
+        <v>45421</v>
       </c>
       <c r="H58" t="n">
-        <v>2843.3</v>
+        <v>2710.1</v>
       </c>
       <c r="I58" t="n">
         <v>2789.850383996675</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K58" t="n">
-        <v>-4.44</v>
+        <v>-8.92</v>
       </c>
       <c r="L58" t="n">
-        <v>5.19</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="M58" t="n">
-        <v>0.45</v>
+        <v>0.54</v>
       </c>
       <c r="N58" t="n">
-        <v>2.39</v>
+        <v>4.68</v>
       </c>
       <c r="O58" t="n">
         <v>3.46</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S58" t="b">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>1</v>
+      </c>
+      <c r="U58" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -3783,22 +4490,22 @@
         <v>10.03</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45447</v>
+        <v>45448</v>
       </c>
       <c r="H59" t="n">
-        <v>2857.65</v>
+        <v>2961.75</v>
       </c>
       <c r="I59" t="n">
         <v>2950.802867003803</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K59" t="n">
-        <v>-5.44</v>
+        <v>-9.289999999999999</v>
       </c>
       <c r="L59" t="n">
-        <v>8.85</v>
+        <v>11.7</v>
       </c>
       <c r="M59" t="n">
         <v>2.39</v>
@@ -3813,7 +4520,19 @@
         <v>1</v>
       </c>
       <c r="Q59" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>8.130000000000001</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45566</v>
+        <v>45568</v>
       </c>
       <c r="H60" t="n">
-        <v>3277.35</v>
+        <v>3149.3</v>
       </c>
       <c r="I60" t="n">
         <v>3195.086311246554</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="K60" t="n">
-        <v>10.66</v>
+        <v>6.33</v>
       </c>
       <c r="L60" t="n">
         <v>4.04</v>
@@ -3861,7 +4580,7 @@
         <v>3.34</v>
       </c>
       <c r="N60" t="n">
-        <v>3.1</v>
+        <v>3.91</v>
       </c>
       <c r="O60" t="n">
         <v>3.64</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>82</v>
+        <v>83</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>5</v>
+      </c>
+      <c r="U60" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="61">
@@ -3897,19 +4628,19 @@
         <v>7.36</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45723</v>
+        <v>45726</v>
       </c>
       <c r="H61" t="n">
-        <v>2270</v>
+        <v>2278.6</v>
       </c>
       <c r="I61" t="n">
         <v>2270.085300995967</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="K61" t="n">
-        <v>27.92</v>
+        <v>27.65</v>
       </c>
       <c r="L61" t="n">
         <v>2.43</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>109</v>
+        <v>110</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>6</v>
+      </c>
+      <c r="U61" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="62">
@@ -3954,19 +4697,19 @@
         <v>6.24</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>45784</v>
+        <v>45785</v>
       </c>
       <c r="H62" t="n">
-        <v>2334.1</v>
+        <v>2302.6</v>
       </c>
       <c r="I62" t="n">
         <v>2311.098594211904</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="K62" t="n">
-        <v>2.44</v>
+        <v>1.05</v>
       </c>
       <c r="L62" t="n">
         <v>3.89</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>3</v>
+      </c>
+      <c r="U62" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="63">
@@ -4011,19 +4766,19 @@
         <v>8.23</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>45834</v>
+        <v>45835</v>
       </c>
       <c r="H63" t="n">
-        <v>2289.8</v>
+        <v>2358.7</v>
       </c>
       <c r="I63" t="n">
         <v>2303.414407093117</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K63" t="n">
-        <v>0.5600000000000001</v>
+        <v>-2.44</v>
       </c>
       <c r="L63" t="n">
         <v>3.31</v>
@@ -4032,7 +4787,7 @@
         <v>1.81</v>
       </c>
       <c r="N63" t="n">
-        <v>2.47</v>
+        <v>3.01</v>
       </c>
       <c r="O63" t="n">
         <v>-1.35</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>3</v>
+      </c>
+      <c r="U63" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="64">
@@ -4068,19 +4835,19 @@
         <v>6.35</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>45856</v>
+        <v>45859</v>
       </c>
       <c r="H64" t="n">
-        <v>2382.4</v>
+        <v>2375.4</v>
       </c>
       <c r="I64" t="n">
         <v>2376.676645034734</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K64" t="n">
-        <v>1</v>
+        <v>0.71</v>
       </c>
       <c r="L64" t="n">
         <v>3.46</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S64" t="b">
+        <v>0</v>
+      </c>
+      <c r="T64" t="n">
+        <v>1</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -4125,28 +4904,28 @@
         <v>5.91</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>45874</v>
+        <v>45875</v>
       </c>
       <c r="H65" t="n">
-        <v>2436.8</v>
+        <v>2491.2</v>
       </c>
       <c r="I65" t="n">
         <v>2454.908148632657</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K65" t="n">
-        <v>-2.58</v>
+        <v>-4.87</v>
       </c>
       <c r="L65" t="n">
-        <v>4.07</v>
+        <v>5.48</v>
       </c>
       <c r="M65" t="n">
         <v>0.5</v>
       </c>
       <c r="N65" t="n">
-        <v>1.78</v>
+        <v>2.23</v>
       </c>
       <c r="O65" t="n">
         <v>-0.29</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>2</v>
+      </c>
+      <c r="U65" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -4182,22 +4973,22 @@
         <v>7.11</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>45922</v>
+        <v>45923</v>
       </c>
       <c r="H66" t="n">
-        <v>2482.7</v>
+        <v>2446.9</v>
       </c>
       <c r="I66" t="n">
         <v>2450.769055063055</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K66" t="n">
-        <v>-0.34</v>
+        <v>-1.78</v>
       </c>
       <c r="L66" t="n">
-        <v>2.06</v>
+        <v>2.54</v>
       </c>
       <c r="M66" t="n">
         <v>0.66</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>2</v>
+      </c>
+      <c r="U66" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -4239,28 +5042,28 @@
         <v>5.15</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>45946</v>
+        <v>45947</v>
       </c>
       <c r="H67" t="n">
-        <v>2409.7</v>
+        <v>2507.8</v>
       </c>
       <c r="I67" t="n">
         <v>2440.174311029059</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K67" t="n">
-        <v>1.52</v>
+        <v>-2.49</v>
       </c>
       <c r="L67" t="n">
-        <v>1.51</v>
+        <v>3.97</v>
       </c>
       <c r="M67" t="n">
         <v>0.51</v>
       </c>
       <c r="N67" t="n">
-        <v>2.46</v>
+        <v>4.07</v>
       </c>
       <c r="O67" t="n">
         <v>-1.44</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>2</v>
+      </c>
+      <c r="U67" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -4296,28 +5111,28 @@
         <v>6.99</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>45999</v>
+        <v>46000</v>
       </c>
       <c r="H68" t="n">
-        <v>2928.3</v>
+        <v>2796</v>
       </c>
       <c r="I68" t="n">
         <v>2807.731668866294</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K68" t="n">
-        <v>16.77</v>
+        <v>11.49</v>
       </c>
       <c r="L68" t="n">
         <v>3.46</v>
       </c>
       <c r="M68" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="N68" t="n">
-        <v>1.35</v>
+        <v>4.52</v>
       </c>
       <c r="O68" t="n">
         <v>4.07</v>
@@ -4326,7 +5141,19 @@
         <v>1</v>
       </c>
       <c r="Q68" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>3</v>
+      </c>
+      <c r="U68" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="69">
@@ -4353,19 +5180,19 @@
         <v>8.380000000000001</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="H69" t="n">
-        <v>2269.6</v>
+        <v>2360.7</v>
       </c>
       <c r="I69" t="n">
         <v>2326.0080908434</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="K69" t="n">
-        <v>18.83</v>
+        <v>15.57</v>
       </c>
       <c r="L69" t="n">
         <v>4.24</v>
@@ -4383,7 +5210,19 @@
         <v>1</v>
       </c>
       <c r="Q69" t="n">
-        <v>82</v>
+        <v>83</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>5</v>
+      </c>
+      <c r="U69" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="70">
@@ -4410,19 +5249,19 @@
         <v>10.97</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="H70" t="n">
-        <v>2631</v>
+        <v>2608.7</v>
       </c>
       <c r="I70" t="n">
         <v>2612.921413962124</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="K70" t="n">
-        <v>11.45</v>
+        <v>10.51</v>
       </c>
       <c r="L70" t="n">
         <v>4.18</v>
@@ -4440,7 +5279,19 @@
         <v>1</v>
       </c>
       <c r="Q70" t="n">
-        <v>96</v>
+        <v>97</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S70" t="b">
+        <v>1</v>
+      </c>
+      <c r="T70" t="n">
+        <v>6</v>
+      </c>
+      <c r="U70" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="71">
@@ -4491,6 +5342,14 @@
       <c r="Q71" t="n">
         <v>41</v>
       </c>
+      <c r="R71" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S71" t="b">
+        <v>1</v>
+      </c>
+      <c r="T71" t="inlineStr"/>
+      <c r="U71" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9449,7 +10308,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>60.1</v>
+        <v>61.5</v>
       </c>
     </row>
     <row r="6">
@@ -9459,7 +10318,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7">
@@ -9469,7 +10328,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="8">
@@ -9479,7 +10338,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -9489,7 +10348,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
     </row>
     <row r="10">
@@ -9499,7 +10358,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="11">
@@ -9509,7 +10368,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12">
@@ -9519,7 +10378,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="13">
@@ -9529,7 +10388,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>36.2</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="14">
@@ -9539,7 +10398,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.86</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="15">
@@ -9549,7 +10408,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6.23</v>
+        <v>3.72</v>
       </c>
     </row>
     <row r="16">
@@ -9559,7 +10418,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.42</v>
+        <v>-0.74</v>
       </c>
     </row>
     <row r="17">
@@ -9569,7 +10428,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>60.64</v>
+        <v>58.27</v>
       </c>
     </row>
     <row r="18">
@@ -9579,7 +10438,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>50.7</v>
+        <v>42</v>
       </c>
     </row>
     <row r="19">
@@ -9589,7 +10448,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4.41</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="20">
@@ -9599,7 +10458,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4.04</v>
+        <v>4.27</v>
       </c>
     </row>
     <row r="21">
@@ -9609,7 +10468,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>11.71</v>
+        <v>13.64</v>
       </c>
     </row>
     <row r="22">
@@ -9619,7 +10478,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
     </row>
     <row r="23">
@@ -9629,7 +10488,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24">
@@ -9639,7 +10498,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.74</v>
+        <v>1.83</v>
       </c>
     </row>
     <row r="25">
@@ -9659,7 +10518,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.17</v>
+        <v>3.69</v>
       </c>
     </row>
     <row r="27">
@@ -9679,7 +10538,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
     </row>
     <row r="29">
